--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-37_temperli_cam_kok_neden_ve_aksiyon_analizi__6m.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-37_temperli_cam_kok_neden_ve_aksiyon_analizi__6m.xlsx
@@ -927,7 +927,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-37&amp;C&amp;"Arial,Regular"&amp;11Temperli Cam Kök Neden ve Aksiyon Analizi - 6M</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: 6M incelemesi kanıta dayalı çalışma formuna çevrildi; HST yalnız uygulanabilir ürün şartına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1061,7 +1062,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-37&amp;C&amp;"Arial,Regular"&amp;11Temperli Cam Kök Neden ve Aksiyon Analizi - 6M</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: 6M incelemesi kanıta dayalı çalışma formuna çevrildi; HST yalnız uygulanabilir ürün şartına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>